--- a/output/full_scan/batch_seq0_2026-10-16.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8046</v>
+        <v>8111</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>609.7109754901157</v>
+        <v>611.2052544437114</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1355</v>
+        <v>83.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.89674914150616</v>
+        <v>53.7680551463751</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.99212367217237</v>
+        <v>35.22727342936467</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8073338761441303</v>
+        <v>0.1029099887992237</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-5.685971988608202</v>
+        <v>-0.88017362422862</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8358</v>
+        <v>8046</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>606.7560047660168</v>
+        <v>609.7109754901157</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>472</v>
+        <v>1355</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,25 +1559,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>44.17089198018133</v>
+        <v>54.89674914150616</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.50330098540359</v>
+        <v>26.99212367217237</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.27742387387842</v>
+        <v>0.8073338761441303</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-8.460898562423143</v>
+        <v>-5.685971988608202</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8996</v>
+        <v>8358</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>604.6347684922082</v>
+        <v>606.7560047660168</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1570</v>
+        <v>472</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.21325523775187</v>
+        <v>44.17089198018133</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>41.60393865052708</v>
+        <v>23.50330098540359</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.734115022971928</v>
+        <v>1.27742387387842</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-13.57034090552668</v>
+        <v>-8.460898562423143</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8150</v>
+        <v>8996</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>604.0069741529261</v>
+        <v>604.6347684922082</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>105.5</v>
+        <v>1570</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.98093152085777</v>
+        <v>54.21325523775187</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>35.67693524300092</v>
+        <v>41.60393865052708</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3360540047583811</v>
+        <v>1.734115022971928</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.895699069434468</v>
+        <v>-13.57034090552668</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8086</v>
+        <v>8150</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>589.635115187773</v>
+        <v>604.0069741529261</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>131</v>
+        <v>105.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.03199172211032</v>
+        <v>46.98093152085777</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.22855192988327</v>
+        <v>35.67693524300092</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7757112389828867</v>
+        <v>0.3360540047583811</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.209826093884418</v>
+        <v>-1.895699069434468</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8277</v>
+        <v>8086</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>545.2559933211708</v>
+        <v>589.635115187773</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>15.4</v>
+        <v>131</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>75.42643803897461</v>
+        <v>55.03199172211032</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>37.66491985651483</v>
+        <v>29.22855192988327</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3346807704374376</v>
+        <v>0.7757112389828867</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1697673790371896</v>
+        <v>1.209826093884418</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8201</v>
+        <v>8084</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>524.5057805818303</v>
+        <v>569.0947194544688</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>15</v>
+        <v>13.95</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.9640394742703</v>
+        <v>13.46163108578916</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>47.12106730537497</v>
+        <v>62.28949400362444</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4098648308926036</v>
+        <v>0.3629087793955763</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.149808611420225</v>
+        <v>-0.7339464876672697</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8462</v>
+        <v>8277</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>522.0654144055363</v>
+        <v>545.2559933211708</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>158</v>
+        <v>15.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.20791088087213</v>
+        <v>75.42643803897461</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>36.40285672102213</v>
+        <v>37.66491985651483</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8536218387083433</v>
+        <v>0.3346807704374376</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1810462832760433</v>
+        <v>-0.1697673790371896</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8045</v>
+        <v>8201</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>519.0532393318084</v>
+        <v>524.5057805818303</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>56.4</v>
+        <v>15</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.91792937115795</v>
+        <v>52.9640394742703</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.84434486562495</v>
+        <v>47.12106730537497</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.174491050702999</v>
+        <v>0.4098648308926036</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1306100715371639</v>
+        <v>-0.149808611420225</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8114</v>
+        <v>8462</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>514.5288105684909</v>
+        <v>522.0654144055363</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.72210431594814</v>
+        <v>47.20791088087213</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>18.52364919687392</v>
+        <v>36.40285672102213</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7505944441222524</v>
+        <v>0.8536218387083433</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.256813622134269</v>
+        <v>0.1810462832760433</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8040</v>
+        <v>8045</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>504.6362080105639</v>
+        <v>519.0532393318084</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>82</v>
+        <v>56.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.22412288986143</v>
+        <v>56.91792937115795</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.6367033647521</v>
+        <v>21.84434486562495</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.1674967880958573</v>
+        <v>1.174491050702999</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.757341582893906</v>
+        <v>0.1306100715371639</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8103</v>
+        <v>8114</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>493.0053255395613</v>
+        <v>514.5288105684909</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>105.5</v>
+        <v>182</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>40.41289668853912</v>
+        <v>49.72210431594814</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.09057710146553</v>
+        <v>18.52364919687392</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.1796687568261508</v>
+        <v>0.7505944441222524</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.745255557096511</v>
+        <v>1.256813622134269</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8383</v>
+        <v>8040</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>490.979412011822</v>
+        <v>504.6362080105639</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.03352175149941</v>
+        <v>44.22412288986143</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.11015663538389</v>
+        <v>21.6367033647521</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5170763333527139</v>
+        <v>0.1674967880958573</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>1</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0456052940232447</v>
+        <v>-1.757341582893906</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8068</v>
+        <v>8103</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>486.8036901537021</v>
+        <v>493.0053255395613</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>18.05</v>
+        <v>105.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.02835511881724</v>
+        <v>40.41289668853912</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.4161864779829</v>
+        <v>28.09057710146553</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6528769761985026</v>
+        <v>0.1796687568261508</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0890909504481591</v>
+        <v>-2.745255557096511</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8097</v>
+        <v>8383</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>482.639281413521</v>
+        <v>490.979412011822</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>48.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>41.03287257131182</v>
+        <v>53.03352175149941</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.43492985875814</v>
+        <v>18.11015663538389</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4184386782918993</v>
+        <v>0.5170763333527139</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0418588490971332</v>
+        <v>0.0456052940232447</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8443</v>
+        <v>8068</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>482.3726681855275</v>
+        <v>486.8036901537021</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11.25</v>
+        <v>18.05</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.96886166125628</v>
+        <v>53.02835511881724</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>42.21184613799809</v>
+        <v>34.4161864779829</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.187831220232105</v>
+        <v>0.6528769761985026</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.06811116614696371</v>
+        <v>0.0890909504481591</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8234</v>
+        <v>8097</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>480.7875857012677</v>
+        <v>482.639281413521</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>63.4</v>
+        <v>48.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.45795573147505</v>
+        <v>41.03287257131182</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.11172543280187</v>
+        <v>14.43492985875814</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.060691758664336</v>
+        <v>0.4184386782918993</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2705158418040025</v>
+        <v>0.0418588490971332</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8182</v>
+        <v>8443</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>472.3018895734327</v>
+        <v>482.3726681855275</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>40</v>
+        <v>11.25</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.8223191251017</v>
+        <v>51.96886166125628</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.56747485468785</v>
+        <v>42.21184613799809</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4486502464353188</v>
+        <v>2.187831220232105</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.3478162214226542</v>
+        <v>0.06811116614696371</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8455</v>
+        <v>8234</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>469.3975960249649</v>
+        <v>480.7875857012677</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>24.2</v>
+        <v>63.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.13458830637119</v>
+        <v>49.45795573147505</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9.7828915662874</v>
+        <v>15.11172543280187</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3843729514396652</v>
+        <v>1.060691758664336</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0047516662073938</v>
+        <v>0.2705158418040025</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8438</v>
+        <v>8182</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>461.8070109397948</v>
+        <v>472.3018895734327</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>71.8</v>
+        <v>40</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>41.26113129830117</v>
+        <v>45.8223191251017</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.30241600758701</v>
+        <v>23.56747485468785</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4231177035839802</v>
+        <v>0.4486502464353188</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.016449548638898</v>
+        <v>-0.3478162214226542</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8074</v>
+        <v>8455</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>461.7506953680126</v>
+        <v>469.3975960249649</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>55.6</v>
+        <v>24.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.75925219276948</v>
+        <v>52.13458830637119</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.79119387534404</v>
+        <v>9.7828915662874</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.914195258163748</v>
+        <v>0.3843729514396652</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2312093734367113</v>
+        <v>0.0047516662073938</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8064</v>
+        <v>8438</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>458.4886562941385</v>
+        <v>461.8070109397948</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>118</v>
+        <v>71.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.2848669889902</v>
+        <v>41.26113129830117</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.464468398563</v>
+        <v>27.30241600758701</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4321724753263447</v>
+        <v>0.4231177035839802</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.342944349005908</v>
+        <v>-1.016449548638898</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8271</v>
+        <v>8074</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>453.0706990652041</v>
+        <v>461.7506953680126</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>187</v>
+        <v>55.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>33.21969222474986</v>
+        <v>53.75925219276948</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.86038144004652</v>
+        <v>21.79119387534404</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6541780922173062</v>
+        <v>0.914195258163748</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.008002394597101</v>
+        <v>0.2312093734367113</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8112</v>
+        <v>8064</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>449.2607675145653</v>
+        <v>458.4886562941385</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>118</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.72028018787562</v>
+        <v>42.2848669889902</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.64397867489888</v>
+        <v>19.464468398563</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.049880764717078</v>
+        <v>0.4321724753263447</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3205114538979139</v>
+        <v>-3.342944349005908</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8101</v>
+        <v>8271</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>447.9534273001101</v>
+        <v>453.0706990652041</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9.99</v>
+        <v>187</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.12749628597864</v>
+        <v>33.21969222474986</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.62101529213902</v>
+        <v>20.86038144004652</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.704718902310234</v>
+        <v>0.6541780922173062</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1045132400002896</v>
+        <v>-1.008002394597101</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8442</v>
+        <v>8112</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>443.2193975359773</v>
+        <v>449.2607675145653</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>48.75</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>66.97502720396011</v>
+        <v>45.72028018787562</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.38817415583105</v>
+        <v>14.64397867489888</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.538130677378876</v>
+        <v>1.049880764717078</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3130884466406469</v>
+        <v>0.3205114538979139</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8110</v>
+        <v>8101</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>436.8979619740717</v>
+        <v>447.9534273001101</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>47</v>
+        <v>9.99</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.16594849769283</v>
+        <v>42.12749628597864</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.64489757554577</v>
+        <v>22.62101529213902</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2364804371159122</v>
+        <v>1.704718902310234</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3575814597122615</v>
+        <v>-0.1045132400002896</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8043</v>
+        <v>8442</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>436.3492706169691</v>
+        <v>443.2193975359773</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>141.5</v>
+        <v>48.75</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.69599616792573</v>
+        <v>66.97502720396011</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.51272238466049</v>
+        <v>19.38817415583105</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.280978480370112</v>
+        <v>0.538130677378876</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.8408720468021363</v>
+        <v>0.3130884466406469</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8071</v>
+        <v>8110</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>427.899301446958</v>
+        <v>436.8979619740717</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>20.9</v>
+        <v>47</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>39.18460004176729</v>
+        <v>49.16594849769283</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.490444980292</v>
+        <v>23.64489757554577</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8259417586715726</v>
+        <v>0.2364804371159122</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0506184249963628</v>
+        <v>-0.3575814597122615</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8162</v>
+        <v>8043</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>426.7030307512218</v>
+        <v>436.3492706169691</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>60.8</v>
+        <v>141.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43.69986063720054</v>
+        <v>51.69599616792573</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.73951999741652</v>
+        <v>18.51272238466049</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2351281317946218</v>
+        <v>1.280978480370112</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.6486247556049591</v>
+        <v>0.8408720468021363</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9110</v>
+        <v>8071</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>419.2305656027117</v>
+        <v>427.899301446958</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>3.03</v>
+        <v>20.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.70130289023454</v>
+        <v>39.18460004176729</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5.010159656685337</v>
+        <v>14.490444980292</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.773463306958089</v>
+        <v>0.8259417586715726</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0007770675919268</v>
+        <v>-0.0506184249963628</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8464</v>
+        <v>8162</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>418.1199980695274</v>
+        <v>426.7030307512218</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>368.5</v>
+        <v>60.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.90111705264525</v>
+        <v>43.69986063720054</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9.279636407875484</v>
+        <v>20.73951999741652</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.694771438883389</v>
+        <v>0.2351281317946218</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4102672810181985</v>
+        <v>-0.6486247556049591</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8926</v>
+        <v>9110</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>410.5870540732699</v>
+        <v>419.2305656027117</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>59</v>
+        <v>3.03</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.04923930225458</v>
+        <v>51.70130289023454</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.91043593985952</v>
+        <v>5.010159656685337</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5304446856054048</v>
+        <v>1.773463306958089</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.011799120640592</v>
+        <v>-0.0007770675919268</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8038</v>
+        <v>8464</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>404.5329659341935</v>
+        <v>418.1199980695274</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>34</v>
+        <v>368.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.97984443223813</v>
+        <v>48.90111705264525</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>31.29723128717979</v>
+        <v>9.279636407875484</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5332897484950068</v>
+        <v>1.694771438883389</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0100642209337125</v>
+        <v>0.4102672810181985</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8227</v>
+        <v>8926</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>399.5626868669158</v>
+        <v>410.5870540732699</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.1966968173459</v>
+        <v>50.04923930225458</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>36.56304635796354</v>
+        <v>13.91043593985952</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.133362645736093</v>
+        <v>0.5304446856054048</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-12.94181044616891</v>
+        <v>-0.011799120640592</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8422</v>
+        <v>8038</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>397.4633968974505</v>
+        <v>404.5329659341935</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>25.7</v>
+        <v>34</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.62533098805338</v>
+        <v>51.97984443223813</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8.329355031658647</v>
+        <v>31.29723128717979</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.067973639998854</v>
+        <v>0.5332897484950068</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0182006766188463</v>
+        <v>0.0100642209337125</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8482</v>
+        <v>8227</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>397.2776219681047</v>
+        <v>399.5626868669158</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>49.1</v>
+        <v>282</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.15762831069969</v>
+        <v>48.1966968173459</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5.500414256718671</v>
+        <v>36.56304635796354</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4811480875310662</v>
+        <v>1.133362645736093</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1188045432252285</v>
+        <v>-12.94181044616891</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8410</v>
+        <v>8422</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>392.1056807521499</v>
+        <v>397.4633968974505</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>27</v>
+        <v>25.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>35.28379849548139</v>
+        <v>49.62533098805338</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>47.32799434457405</v>
+        <v>8.329355031658647</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.237405047381435</v>
+        <v>1.067973639998854</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0266865468266785</v>
+        <v>0.0182006766188463</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8440</v>
+        <v>8482</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>388.1916192547457</v>
+        <v>397.2776219681047</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>19.95</v>
+        <v>49.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.80995101758576</v>
+        <v>51.15762831069969</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.20952110087241</v>
+        <v>5.500414256718671</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6330129256303049</v>
+        <v>0.4811480875310662</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.026043575111736</v>
+        <v>0.1188045432252285</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8096</v>
+        <v>8410</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>382.6536553277968</v>
+        <v>392.1056807521499</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>85.3</v>
+        <v>27</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>37.67357100498213</v>
+        <v>35.28379849548139</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>29.90075663604702</v>
+        <v>47.32799434457405</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4710821177263296</v>
+        <v>0.237405047381435</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.7834473801008901</v>
+        <v>0.0266865468266785</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8102</v>
+        <v>8440</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>380.3661036822512</v>
+        <v>388.1916192547457</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>59</v>
+        <v>19.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.57171792043147</v>
+        <v>44.80995101758576</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3.820903781776791</v>
+        <v>22.20952110087241</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2963234723466702</v>
+        <v>0.6330129256303049</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.7764992792803226</v>
+        <v>-0.026043575111736</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8367</v>
+        <v>8096</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>377.0587861837478</v>
+        <v>382.6536553277968</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>41.35</v>
+        <v>85.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>56.06593675576948</v>
+        <v>37.67357100498213</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.70494413619651</v>
+        <v>29.90075663604702</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.760924799722738</v>
+        <v>0.4710821177263296</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,51 +3697,51 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0891061389956687</v>
+        <v>0.7834473801008901</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8047</v>
+        <v>8102</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>369.6497012691827</v>
+        <v>380.3661036822512</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>44.4</v>
+        <v>59</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.18577418256634</v>
+        <v>50.57171792043147</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7.474352730921065</v>
+        <v>3.820903781776791</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6480589829337459</v>
+        <v>0.2963234723466702</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.003918340993527</v>
+        <v>0.7764992792803226</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8423</v>
+        <v>8367</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>368.4217738136678</v>
+        <v>377.0587861837478</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>18.05</v>
+        <v>41.35</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.59341557515714</v>
+        <v>56.06593675576948</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.52610563479467</v>
+        <v>16.70494413619651</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.940255654386986</v>
+        <v>0.760924799722738</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,84 +3803,84 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0073968265436412</v>
+        <v>0.0891061389956687</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8299</v>
+        <v>8047</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>368.2904787444509</v>
+        <v>369.6497012691827</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1890</v>
+        <v>44.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.25561424951623</v>
+        <v>50.18577418256634</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.64589797809953</v>
+        <v>7.474352730921065</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.999532850847922</v>
+        <v>0.6480589829337459</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-28.51942606477036</v>
+        <v>-0.003918340993527</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8093</v>
+        <v>8423</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>368.2829505736724</v>
+        <v>368.4217738136678</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>27</v>
+        <v>18.05</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.79768699796273</v>
+        <v>53.59341557515714</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.81446243971119</v>
+        <v>26.52610563479467</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5369549528981792</v>
+        <v>0.940255654386986</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2154074307662967</v>
+        <v>0.0073968265436412</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8411</v>
+        <v>8299</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>360.2446631203947</v>
+        <v>368.2904787444509</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11.1</v>
+        <v>1890</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,66 +3944,66 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>20.16522907115552</v>
+        <v>37.25561424951623</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>44.0590424112837</v>
+        <v>14.64589797809953</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.519534304646664</v>
+        <v>0.999532850847922</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0502086096074672</v>
+        <v>-28.51942606477036</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8183</v>
+        <v>8093</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>355.8634049635203</v>
+        <v>368.2829505736724</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G67" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.90268855459766</v>
+        <v>54.79768699796273</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.14537627929968</v>
+        <v>14.81446243971119</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.5369549528981792</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0686206100730056</v>
+        <v>0.2154074307662967</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>9912</v>
+        <v>8411</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>346.1790704485379</v>
+        <v>360.2446631203947</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>13</v>
+        <v>11.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.83549957795234</v>
+        <v>20.16522907115552</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>29.51079757760742</v>
+        <v>44.0590424112837</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6709325180170342</v>
+        <v>2.519534304646664</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,48 +4068,48 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0539810490923521</v>
+        <v>-0.0502086096074672</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8131</v>
+        <v>8183</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>340.8914378906725</v>
+        <v>355.8634049635203</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>63.5</v>
+        <v>28.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.65420081392246</v>
+        <v>44.90268855459766</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.3556402610324</v>
+        <v>19.14537627929968</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6328229989660987</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1082840198174168</v>
+        <v>0.0686206100730056</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8467</v>
+        <v>9912</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>332.4621468244385</v>
+        <v>346.1790704485379</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>60.71369469216457</v>
+        <v>51.83549957795234</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.29945762650226</v>
+        <v>29.51079757760742</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.046214682443854</v>
+        <v>0.6709325180170342</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.067767165368887</v>
+        <v>0.0539810490923521</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8104</v>
+        <v>8131</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>327.164883529382</v>
+        <v>340.8914378906725</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>29.9</v>
+        <v>63.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.36074224978701</v>
+        <v>49.65420081392246</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.21547297505151</v>
+        <v>19.3556402610324</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6235024792455542</v>
+        <v>0.6328229989660987</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1244671501782063</v>
+        <v>0.1082840198174168</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8076</v>
+        <v>8467</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>326.7918337507519</v>
+        <v>332.4621468244385</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.9</v>
+        <v>102</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.30012269448477</v>
+        <v>60.71369469216457</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.21575977035709</v>
+        <v>16.29945762650226</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5547533572594342</v>
+        <v>2.046214682443854</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0248030863637992</v>
+        <v>2.067767165368887</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8147</v>
+        <v>8104</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>325.3137615457419</v>
+        <v>327.164883529382</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>130.5</v>
+        <v>29.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.00144645254182</v>
+        <v>40.36074224978701</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>28.24513985699462</v>
+        <v>14.21547297505151</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5574753154510479</v>
+        <v>0.6235024792455542</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.560522200306751</v>
+        <v>-0.1244671501782063</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8249</v>
+        <v>8076</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>318.4145969167418</v>
+        <v>326.7918337507519</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>39.95</v>
+        <v>20.9</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.46078919310254</v>
+        <v>40.30012269448477</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.13831609034802</v>
+        <v>29.21575977035709</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7934119569729972</v>
+        <v>0.5547533572594342</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1324780281678491</v>
+        <v>-0.0248030863637992</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8477</v>
+        <v>8147</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>316.8674075266987</v>
+        <v>325.3137615457419</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>13.7</v>
+        <v>130.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>35.67978498419457</v>
+        <v>44.00144645254182</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>35.64530827105482</v>
+        <v>28.24513985699462</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.700392732753332</v>
+        <v>0.5574753154510479</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0082377779733575</v>
+        <v>-1.560522200306751</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8404</v>
+        <v>8249</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>314.9008905562637</v>
+        <v>318.4145969167418</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>13.7</v>
+        <v>39.95</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.25468128920468</v>
+        <v>50.46078919310254</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>34.89944014526331</v>
+        <v>14.13831609034802</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5728037796423167</v>
+        <v>0.7934119569729972</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1200482137928962</v>
+        <v>0.1324780281678491</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8940</v>
+        <v>8477</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>314.7479484245176</v>
+        <v>316.8674075266987</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>15.05</v>
+        <v>13.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.29637083031395</v>
+        <v>35.67978498419457</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.00537218719721</v>
+        <v>35.64530827105482</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4289710497697669</v>
+        <v>1.700392732753332</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0194286238794387</v>
+        <v>-0.0082377779733575</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8048</v>
+        <v>8404</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>310.9834339125966</v>
+        <v>314.9008905562637</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>51.5</v>
+        <v>13.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.38922234521992</v>
+        <v>45.25468128920468</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.59956511113211</v>
+        <v>34.89944014526331</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5377218536217245</v>
+        <v>0.5728037796423167</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2011128819650535</v>
+        <v>0.1200482137928962</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8087</v>
+        <v>8940</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>309.5826372699713</v>
+        <v>314.7479484245176</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>22.7</v>
+        <v>15.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.66519229384902</v>
+        <v>49.29637083031395</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4.659186670578379</v>
+        <v>13.00537218719721</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.459913064297622</v>
+        <v>0.4289710497697669</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0047825831873163</v>
+        <v>0.0194286238794387</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8210</v>
+        <v>8048</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>303.2685904524865</v>
+        <v>310.9834339125966</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>834</v>
+        <v>51.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>37.04770430018669</v>
+        <v>52.38922234521992</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.04652728164053</v>
+        <v>12.59956511113211</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3675361907094615</v>
+        <v>0.5377218536217245</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.370093842866659</v>
+        <v>0.2011128819650535</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8155</v>
+        <v>8087</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>298.2133766379071</v>
+        <v>309.5826372699713</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>302</v>
+        <v>22.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.80929860957409</v>
+        <v>47.66519229384902</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.59484254729033</v>
+        <v>4.659186670578379</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.627307306541194</v>
+        <v>1.459913064297622</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-2.345688292694303</v>
+        <v>-0.0047825831873163</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8088</v>
+        <v>8210</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>292.4682690619384</v>
+        <v>303.2685904524865</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>42.85</v>
+        <v>834</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.56109089562658</v>
+        <v>37.04770430018669</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.01036032570862</v>
+        <v>21.04652728164053</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5552365883859497</v>
+        <v>0.3675361907094615</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0576936831666842</v>
+        <v>1.370093842866659</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8121</v>
+        <v>8155</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>288.3237416712678</v>
+        <v>298.2133766379071</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>31.3</v>
+        <v>302</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.41534772788726</v>
+        <v>39.80929860957409</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>31.25260242320005</v>
+        <v>12.59484254729033</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3324098273280272</v>
+        <v>0.627307306541194</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0900241328769031</v>
+        <v>-2.345688292694303</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8085</v>
+        <v>8088</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>287.7318767849381</v>
+        <v>292.4682690619384</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>14.3</v>
+        <v>42.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.78556564188044</v>
+        <v>45.56109089562658</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.96249899068341</v>
+        <v>15.01036032570862</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7871044918021077</v>
+        <v>0.5552365883859497</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>1</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.09415122190744959</v>
+        <v>0.0576936831666842</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8463</v>
+        <v>8121</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>283.5529030482617</v>
+        <v>288.3237416712678</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>21.3</v>
+        <v>31.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.52725171767923</v>
+        <v>51.41534772788726</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.97453051167785</v>
+        <v>31.25260242320005</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5343567138798555</v>
+        <v>0.3324098273280272</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0255055555061308</v>
+        <v>-0.0900241328769031</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8091</v>
+        <v>8085</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>282.7174877578197</v>
+        <v>287.7318767849381</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>209</v>
+        <v>14.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.82345919315242</v>
+        <v>47.78556564188044</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.516250899056</v>
+        <v>18.96249899068341</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5804874923142214</v>
+        <v>0.7871044918021077</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.420020467268146</v>
+        <v>-0.09415122190744959</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8072</v>
+        <v>8463</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>282.3346094821629</v>
+        <v>283.5529030482617</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>26.5</v>
+        <v>21.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.48994972010244</v>
+        <v>51.52725171767923</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28.1579370247057</v>
+        <v>24.97453051167785</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5768615494093161</v>
+        <v>0.5343567138798555</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1367892757173558</v>
+        <v>0.0255055555061308</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8059</v>
+        <v>8091</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>282.2335551745416</v>
+        <v>282.7174877578197</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>17.25</v>
+        <v>209</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.97498416841049</v>
+        <v>40.82345919315242</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.15804300995742</v>
+        <v>16.516250899056</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3547393876500996</v>
+        <v>0.5804874923142214</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0986861011867799</v>
+        <v>-1.420020467268146</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8908</v>
+        <v>8072</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>280.8642278537412</v>
+        <v>282.3346094821629</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.2</v>
+        <v>26.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.97361629717842</v>
+        <v>43.48994972010244</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.22478439315003</v>
+        <v>28.1579370247057</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.760617295114085</v>
+        <v>0.5768615494093161</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0055654508424161</v>
+        <v>-0.1367892757173558</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8466</v>
+        <v>8059</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>274.1003720221849</v>
+        <v>282.2335551745416</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.95</v>
+        <v>17.25</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.75247776547548</v>
+        <v>53.97498416841049</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.59047738358864</v>
+        <v>27.15804300995742</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.17852969644084</v>
+        <v>0.3547393876500996</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0055465098044826</v>
+        <v>-0.0986861011867799</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8499</v>
+        <v>8908</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>268.4289494759778</v>
+        <v>280.8642278537412</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>238</v>
+        <v>40.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.56198379058287</v>
+        <v>53.97361629717842</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6.976836818320277</v>
+        <v>15.22478439315003</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.657289638548769</v>
+        <v>0.760617295114085</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.6087057088195251</v>
+        <v>-0.0055654508424161</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8487</v>
+        <v>8466</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>250.0313841627159</v>
+        <v>274.1003720221849</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69</v>
+        <v>14.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>36.03368319069035</v>
+        <v>45.75247776547548</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.94899386113522</v>
+        <v>20.59047738358864</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9552041012049034</v>
+        <v>1.17852969644084</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0828654193782169</v>
+        <v>0.0055465098044826</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8049</v>
+        <v>8499</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>245.863309049971</v>
+        <v>268.4289494759778</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>24.25</v>
+        <v>238</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.36922723562283</v>
+        <v>46.56198379058287</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.9193145922191</v>
+        <v>6.976836818320277</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6991065561523272</v>
+        <v>1.657289638548769</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0104554910941715</v>
+        <v>-0.6087057088195251</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8176</v>
+        <v>8487</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>244.5867134366458</v>
+        <v>250.0313841627159</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>69</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.48506822328651</v>
+        <v>36.03368319069035</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.49110122283923</v>
+        <v>11.94899386113522</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.250645990729907</v>
+        <v>0.9552041012049034</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0001171961937788</v>
+        <v>-0.0828654193782169</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8932</v>
+        <v>8049</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>242.3679981506266</v>
+        <v>245.8633090499709</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>89.59999999999999</v>
+        <v>24.25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,49 +5481,49 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.01611718433085</v>
+        <v>40.36922723562283</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.74571870273761</v>
+        <v>12.9193145922191</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.368838393652234</v>
+        <v>0.6991065561523272</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.3094860596451223</v>
+        <v>-0.0104554910941715</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8222</v>
+        <v>8176</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>241.8522049429928</v>
+        <v>244.5867134366458</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>34.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.42080172465604</v>
+        <v>52.48506822328651</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.364335519759962</v>
+        <v>22.49110122283923</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.526016649335072</v>
+        <v>2.250645990729907</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0529845688514503</v>
+        <v>-0.0001171961937788</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8054</v>
+        <v>8932</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>241.5489504226881</v>
+        <v>242.3679981506266</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>75.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>35.07256904574507</v>
+        <v>42.01611718433085</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.49369644642661</v>
+        <v>15.74571870273761</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4802083760343885</v>
+        <v>1.368838393652234</v>
       </c>
       <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M97" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.266719474433022</v>
+        <v>0.3094860596451223</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8291</v>
+        <v>8222</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>240.8405595762128</v>
+        <v>241.8522049429928</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>21.45</v>
+        <v>34.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>21.9004675425039</v>
+        <v>41.42080172465604</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.31040130353724</v>
+        <v>8.364335519759962</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.234462645870122</v>
+        <v>1.526016649335072</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.4645296824248954</v>
+        <v>0.0529845688514503</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8092</v>
+        <v>8054</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>237.6677518221621</v>
+        <v>241.5489504226881</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>12.3</v>
+        <v>75.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.51248383069498</v>
+        <v>35.07256904574507</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.66670015134865</v>
+        <v>18.49369644642661</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2973501551438989</v>
+        <v>0.4802083760343885</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0121525398419081</v>
+        <v>-1.266719474433022</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8390</v>
+        <v>8291</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>234.7196099417197</v>
+        <v>240.8405595762128</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>89.7</v>
+        <v>21.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.64388749578839</v>
+        <v>21.9004675425039</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.82688263295545</v>
+        <v>12.31040130353724</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7547734618144091</v>
+        <v>2.234462645870122</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.2055436032219453</v>
+        <v>-0.4645296824248954</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8261</v>
+        <v>8092</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>231.8475322170558</v>
+        <v>237.6677518221621</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>160</v>
+        <v>12.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.71856144268364</v>
+        <v>41.51248383069498</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.62820260380118</v>
+        <v>14.66670015134865</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3099558422958181</v>
+        <v>0.2973501551438989</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-2.354265739440458</v>
+        <v>0.0121525398419081</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>9930</v>
+        <v>8390</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>230.4892515484601</v>
+        <v>234.7196099417197</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>59.5</v>
+        <v>89.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.35586047410506</v>
+        <v>41.64388749578839</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>30.25421351647922</v>
+        <v>16.82688263295545</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6914778013180833</v>
+        <v>0.7547734618144091</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1011190587649032</v>
+        <v>0.2055436032219453</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8472</v>
+        <v>8261</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>224.0687943154336</v>
+        <v>231.8475322170558</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>65.5</v>
+        <v>160</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.98646317956605</v>
+        <v>38.71856144268364</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>30.88165325514605</v>
+        <v>16.62820260380118</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.0431127398146152</v>
+        <v>0.3099558422958181</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.6871479880084781</v>
+        <v>-2.354265739440458</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8080</v>
+        <v>9930</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.9990464918252</v>
+        <v>230.4892515484601</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>27.6</v>
+        <v>59.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.79398631114934</v>
+        <v>39.35586047410506</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>23.72181553514457</v>
+        <v>30.25421351647922</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.1999046491825209</v>
+        <v>0.6914778013180833</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.3372052071721335</v>
+        <v>0.1011190587649032</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9136</v>
+        <v>8472</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>197.7464107003032</v>
+        <v>224.0687943154336</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>8.77</v>
+        <v>65.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>26.76497423935719</v>
+        <v>37.98646317956605</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.43234662303115</v>
+        <v>30.88165325514605</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.25267601917009</v>
+        <v>0.0431127398146152</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0355963073668078</v>
+        <v>-0.6871479880084781</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8429</v>
+        <v>8080</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>192.5307449871262</v>
+        <v>217.9990464918252</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>5.87</v>
+        <v>27.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.35410304707695</v>
+        <v>50.79398631114934</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.571883766973258</v>
+        <v>23.72181553514457</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.418457283160957</v>
+        <v>0.1999046491825209</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0035166058310521</v>
+        <v>0.3372052071721335</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8374</v>
+        <v>9136</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>176.3932033273492</v>
+        <v>197.7464107003032</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>71.5</v>
+        <v>8.77</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.17161414742698</v>
+        <v>26.76497423935719</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.60472596809853</v>
+        <v>16.43234662303115</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5353989738192159</v>
+        <v>1.25267601917009</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3647746787552601</v>
+        <v>0.0355963073668078</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8067</v>
+        <v>8429</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>173.2235731379408</v>
+        <v>192.5307449871262</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>10.8</v>
+        <v>5.87</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.63780303724041</v>
+        <v>39.35410304707695</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.87644479673423</v>
+        <v>8.571883766973258</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1236702648558206</v>
+        <v>0.418457283160957</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0467728933677065</v>
+        <v>0.0035166058310521</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8478</v>
+        <v>8374</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>165.8142804916965</v>
+        <v>176.3932033273492</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>138.5</v>
+        <v>71.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.47587096762881</v>
+        <v>33.17161414742698</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.3541444367175</v>
+        <v>15.60472596809853</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.773617475078853</v>
+        <v>0.5353989738192159</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0084747187218309</v>
+        <v>-0.3647746787552601</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8488</v>
+        <v>8067</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>141.2507199842658</v>
+        <v>173.2235731379408</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9.57</v>
+        <v>10.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.84460425626541</v>
+        <v>36.63780303724041</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.93417501157954</v>
+        <v>18.87644479673423</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.127223832840606</v>
+        <v>0.1236702648558206</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0749802100687435</v>
+        <v>-0.0467728933677065</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9955</v>
+        <v>8478</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>139.5828408120602</v>
+        <v>165.8142804916965</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>22.65</v>
+        <v>138.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.63708106657028</v>
+        <v>40.47587096762881</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.73103317247834</v>
+        <v>10.3541444367175</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8263915000540186</v>
+        <v>0.773617475078853</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0325890222050453</v>
+        <v>-0.0084747187218309</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8341</v>
+        <v>8488</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>139.181919833534</v>
+        <v>141.2507199842658</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.48556814916891</v>
+        <v>50.84460425626541</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.34942961262934</v>
+        <v>28.93417501157954</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.096449400492192</v>
+        <v>0.127223832840606</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1010766003677897</v>
+        <v>0.0749802100687435</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8163</v>
+        <v>9955</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>133.6468474927816</v>
+        <v>139.5828408120602</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>29</v>
+        <v>22.65</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.28137802606145</v>
+        <v>38.63708106657028</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.57529749760128</v>
+        <v>12.73103317247834</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6905154442296155</v>
+        <v>0.8263915000540186</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.08229069644111001</v>
+        <v>-0.0325890222050453</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8481</v>
+        <v>8341</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>124.3900542661881</v>
+        <v>139.181919833534</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>40.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.73707993593884</v>
+        <v>51.48556814916891</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.70530170908274</v>
+        <v>13.34942961262934</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.2722387846546584</v>
+        <v>1.096449400492192</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.009145518886163001</v>
+        <v>0.1010766003677897</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8105</v>
+        <v>8163</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>113.3450439868531</v>
+        <v>133.6468474927816</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.61972921914023</v>
+        <v>38.28137802606145</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.69325804846057</v>
+        <v>15.57529749760128</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5120444370642907</v>
+        <v>0.6905154442296155</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0213944606529222</v>
+        <v>-0.08229069644111001</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,52 +6569,158 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>8481</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>政伸</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>124.3900542661881</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46.73707993593884</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>16.70530170908274</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.2722387846546584</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.009145518886163001</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>凌巨</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>113.3450439868531</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>42.61972921914023</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>14.69325804846057</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.5120444370642907</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0213944606529222</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>8473</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>山林水</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>78.9144183887324</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>38.6</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>39.42262133485959</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>19.82903454785133</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.578152163451459</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>0.0867262565900266</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
